--- a/content/post/drafts/weekly-picks/2025Ruka/ladies-points.xlsx
+++ b/content/post/drafts/weekly-picks/2025Ruka/ladies-points.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="397">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -41,6 +41,24 @@
     <t xml:space="preserve">Total_Points</t>
   </si>
   <si>
+    <t xml:space="preserve">Jessie Diggins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1866657053301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1804773016437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.4837270812224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.850870088196</t>
+  </si>
+  <si>
     <t xml:space="preserve">Therese Johaug</t>
   </si>
   <si>
@@ -77,6 +95,54 @@
     <t xml:space="preserve">176.433185878821</t>
   </si>
   <si>
+    <t xml:space="preserve">Frida Karlsson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.2027155548745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3881589061507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2329741353458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.823848596371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ebba Andersson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.7726259215564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0025365955313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3339039374151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.109066454503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosie Brennan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6982578381954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7813210684529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.114864179351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.594443085999</t>
+  </si>
+  <si>
     <t xml:space="preserve">Krista Pärmäkoski</t>
   </si>
   <si>
@@ -92,6 +158,39 @@
     <t xml:space="preserve">147.785697711092</t>
   </si>
   <si>
+    <t xml:space="preserve">Victoria Carl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.0037288919872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2643633636339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.789340501309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.05743275693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katharina Hennig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7069756049925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.610334659603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3672543115808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.684564576176</t>
+  </si>
+  <si>
     <t xml:space="preserve">Johanna Matintalo</t>
   </si>
   <si>
@@ -107,6 +206,21 @@
     <t xml:space="preserve">135.855584268851</t>
   </si>
   <si>
+    <t xml:space="preserve">Jonna Sundling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4081168215604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9546255336323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4878053362589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.850547691452</t>
+  </si>
+  <si>
     <t xml:space="preserve">Heidi Weng</t>
   </si>
   <si>
@@ -119,6 +233,24 @@
     <t xml:space="preserve">130.204171802345</t>
   </si>
   <si>
+    <t xml:space="preserve">Teresa Stadlober</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.4409439815829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1506863128748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9703152846721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.56194557913</t>
+  </si>
+  <si>
     <t xml:space="preserve">Astrid Øyre Slind</t>
   </si>
   <si>
@@ -146,6 +278,81 @@
     <t xml:space="preserve">101.303135332004</t>
   </si>
   <si>
+    <t xml:space="preserve">Nadine Fähndrich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switzerland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.192212091604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3335836477394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5257957393434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delphine Claudel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3878293340857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58949128264524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4414360866402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4187567033712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maja Dahlqvist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.3197221626229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1293024014614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4490245640843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sophia Laukli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1858808890776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95546406476752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7638382702879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9051832241329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linn Svahn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5641268148047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6467969078394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65100859513019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8619323177743</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tiril Udnes Weng</t>
   </si>
   <si>
@@ -212,18 +419,171 @@
     <t xml:space="preserve">68.6842177843071</t>
   </si>
   <si>
+    <t xml:space="preserve">Katerina Janatova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czechia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8036942690328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3047214036058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0978351754783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2062508481169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johanna Hagström</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3316933646697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84316531882518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1748586834949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emma Ribom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1811441371637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0175062832809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5069266507583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7055770712029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moa Ilar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5564382933023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8891784056279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4456166989302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flora Dolci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5028365276629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30654414259781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6829000177084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.4922806879692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pia Fink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8479202308955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81918880229528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5953406351831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.2624496683739</t>
+  </si>
+  <si>
     <t xml:space="preserve">Julie Myhre</t>
   </si>
   <si>
     <t xml:space="preserve">58.1902735873559</t>
   </si>
   <si>
+    <t xml:space="preserve">Caterina Ganz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0626997729214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9084171800726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9321841154259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9033010684198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eva Urevc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6683053994398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4140431171777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5483603317947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6307088484121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julia Kern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88202153339065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.318412025805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2422713182569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4427048774525</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anna Svendsen</t>
   </si>
   <si>
     <t xml:space="preserve">50.3304123876479</t>
   </si>
   <si>
+    <t xml:space="preserve">Laura Gimmler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1602676582945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6582393236582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57151909205403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.3900260740067</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jasmin Kähärä</t>
   </si>
   <si>
@@ -239,12 +599,111 @@
     <t xml:space="preserve">46.113710703638</t>
   </si>
   <si>
+    <t xml:space="preserve">Sofie Krehl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0736718617305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8925963861975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.966268247928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nadja Kälin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5153474995435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6536112511615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3228769994762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4918357501812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kathrine Stewart-Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5436016806224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85130486134523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.844343658367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2392502003346</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ane Appelkvist Stenseth</t>
   </si>
   <si>
     <t xml:space="preserve">39.9664756052368</t>
   </si>
   <si>
+    <t xml:space="preserve">Nicole Monsorno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6524033327357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66427434968176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3166776824174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anja Weber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.319071184153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0170157169424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19644880933393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5325357104294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katherine Sauerbrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8007441013787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33767138332315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71807842668841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8564939113903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisa Lohmann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7340937103877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3772694646279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1113631750156</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hedda Østberg Amundsen</t>
   </si>
   <si>
@@ -263,6 +722,21 @@
     <t xml:space="preserve">31.3035486545315</t>
   </si>
   <si>
+    <t xml:space="preserve">Francesca Franchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08884493506456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85490077780901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9415619954171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8853077082907</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anni Alakoski</t>
   </si>
   <si>
@@ -278,6 +752,48 @@
     <t xml:space="preserve">27.2072238091715</t>
   </si>
   <si>
+    <t xml:space="preserve">Desiree Steiner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71590933007489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0725218382873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57580342205383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.364234590416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helen Hoffmann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3316112525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5440105755742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8756218281133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juliette Ducordeau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43582524785748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85806599339541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7286955752136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0225868164665</t>
+  </si>
+  <si>
     <t xml:space="preserve">Eveliina Piippo</t>
   </si>
   <si>
@@ -290,31 +806,145 @@
     <t xml:space="preserve">22.730823982568</t>
   </si>
   <si>
+    <t xml:space="preserve">Melissa Gal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39481789560249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3729707603707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25116051614762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0189491721208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coletta Rydzek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0600434905039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86650837537224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02683579418623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9533876600624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbora Antosova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2990382609457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66711644969363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9661547106393</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tiia Olkkonen</t>
   </si>
   <si>
     <t xml:space="preserve">20.9114672651301</t>
   </si>
   <si>
+    <t xml:space="preserve">Nora Sanness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6321147622695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anna Comarella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10642294338102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03430404583511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47220321667757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6129302058937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liliane Gagnon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.89306493940642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99799256041574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95897075496758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0638983759769</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nora Kytäjä</t>
   </si>
   <si>
-    <t xml:space="preserve">0.8629044494681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57184223262778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36839071172658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8031373938225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nora Sanness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2782748498399</t>
+    <t xml:space="preserve">1.31291417671395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39795763659292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3779882630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Märta Rosenberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06716199869954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51679588459354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1625533883135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7465112716066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anja Mandeljc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.72963767364509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15164756711344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28697469964535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7089845931137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sydney Palmer-Leger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30471514501506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01208126779249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93017470166391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24697111447145</t>
   </si>
   <si>
     <t xml:space="preserve">Emmi Lämsä</t>
@@ -323,142 +953,256 @@
     <t xml:space="preserve">8.26541967304588</t>
   </si>
   <si>
+    <t xml:space="preserve">Haley Brewster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77501594518944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37302219549283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0082669293794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15630507006167</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oona Kettunen</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.105664973908118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26272573781847</t>
+    <t xml:space="preserve">0.344344753337726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01146120303135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fanny Kukonlehto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48622697681311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosie Fordham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06794542701618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29177727898995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35972270600612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vilma Nissinen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.233748889400793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72459449577808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49084560637728</t>
   </si>
   <si>
     <t xml:space="preserve">Ella-Noora Haapalehto</t>
   </si>
   <si>
-    <t xml:space="preserve">Fanny Kukonlehto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48622697681311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vilma Nissinen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.233748889400793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72459449577808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49084560637728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frida Karlsson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linn Svahn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonna Sundling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victoria Carl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ebba Andersson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emma Ribom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katharina Hennig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moa Ilar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maja Dahlqvist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nadine Fähndrich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switzerland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katerina Janatova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czechia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johanna Hagström</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laura Gimmler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caterina Ganz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Italy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pia Fink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coletta Rydzek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisa Lohmann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desiree Steiner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katherine Sauerbrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sofie Krehl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nadja Kälin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anja Weber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Märta Rosenberg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anna Comarella</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbora Antosova</t>
+    <t xml:space="preserve">Teesi Tuul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.3191225889495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80873915452093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15212039848492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64173696405635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kamila YELGAZINOVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yelizaveta NOPRIIENKO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anastasiia Nikon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ukraine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.07566363866445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89562494997936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14993240488253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.969893716197443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elsa Torvinen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.175962770175843</t>
   </si>
   <si>
     <t xml:space="preserve">Barbora Havlickova</t>
   </si>
   <si>
-    <t xml:space="preserve">Helen Hoffmann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicole Monsorno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francesca Franchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elsa Torvinen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.625972497421694</t>
+    <t xml:space="preserve">-2.80981013926786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6604078674652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335559479997712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.813842791804943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alayna Sonnesyn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10.7356841725455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03119809319374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381970249240256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9.32251583011153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angelina Shuryga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kazakhstan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10.7879541015177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69916890824031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.76503695470362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-11.853822147981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitija Auzina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-14.8844441835301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55075517758024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.28899508869889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-16.6226840946488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darya Ryazhko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-14.836643303959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89472438896276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.68971126949382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-19.6316301844901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katya Galstyan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-14.6821365329454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.319258260812212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.48164958909061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-21.4830443828482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viktoriya Olekh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-17.1278513639015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.06395545245009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.850857267663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-25.0426640840146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kseniya Shalygina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-21.4599065053224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.56328091768424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.66125332302153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-25.6844407460282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nadezhda Stepashkina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-23.4238336897355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.537505066642002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.76574664452997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-28.6520752676235</t>
   </si>
 </sst>
 </file>
@@ -833,7 +1577,7 @@
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -862,7 +1606,7 @@
         <v>18</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="s">
         <v>19</v>
@@ -879,1652 +1623,2460 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.753466546065431</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.753466546065431</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.753466546065431</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0.753466546065431</v>
       </c>
       <c r="I10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.457000561256465</v>
       </c>
       <c r="G12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0.457000561256465</v>
       </c>
       <c r="I12" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.277184851907928</v>
       </c>
       <c r="G21" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0.168121111090064</v>
       </c>
       <c r="I21" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="B22" t="s">
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B23" t="s">
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>118</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>132</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.622459331201855</v>
       </c>
       <c r="G27" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0.622459331201855</v>
       </c>
       <c r="I27" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>12</v>
+        <v>143</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>12</v>
+        <v>147</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.168121111090064</v>
       </c>
       <c r="G29" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0.277184851907928</v>
       </c>
       <c r="I29" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>12</v>
+        <v>151</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>155</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>12</v>
+        <v>156</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.406145296366207</v>
       </c>
       <c r="G31" t="s">
-        <v>12</v>
+        <v>157</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>12</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>115</v>
+        <v>159</v>
       </c>
       <c r="B32" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>160</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>12</v>
+        <v>161</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.457000561256465</v>
       </c>
       <c r="G32" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>0.457000561256465</v>
       </c>
       <c r="I32" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="B34" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>168</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>12</v>
+        <v>169</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>12</v>
+        <v>170</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.614391771436997</v>
       </c>
       <c r="I34" t="s">
-        <v>12</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="B35" t="s">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="C35" t="s">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>12</v>
+        <v>175</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>12</v>
+        <v>176</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>12</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>120</v>
+        <v>178</v>
       </c>
       <c r="B36" t="s">
-        <v>114</v>
+        <v>10</v>
       </c>
       <c r="C36" t="s">
-        <v>12</v>
+        <v>179</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>12</v>
+        <v>180</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.633700227115744</v>
       </c>
       <c r="G36" t="s">
-        <v>12</v>
+        <v>181</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>0.633700227115744</v>
       </c>
       <c r="I36" t="s">
-        <v>12</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>121</v>
+        <v>183</v>
       </c>
       <c r="B37" t="s">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>12</v>
+        <v>184</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>12</v>
+        <v>184</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>122</v>
+        <v>185</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>186</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>12</v>
+        <v>187</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>0.277184851907928</v>
       </c>
       <c r="G38" t="s">
-        <v>12</v>
+        <v>188</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>0.168121111090064</v>
       </c>
       <c r="I38" t="s">
-        <v>12</v>
+        <v>189</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>123</v>
+        <v>190</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>191</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>12</v>
+        <v>192</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>12</v>
+        <v>193</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>12</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>124</v>
+        <v>195</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>49</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>12</v>
+        <v>196</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>12</v>
+        <v>197</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>12</v>
+        <v>198</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>126</v>
+        <v>199</v>
       </c>
       <c r="B41" t="s">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>200</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>12</v>
+        <v>202</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>12</v>
+        <v>203</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>128</v>
+        <v>204</v>
       </c>
       <c r="B42" t="s">
-        <v>114</v>
+        <v>205</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>206</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="s">
-        <v>12</v>
+        <v>207</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>12</v>
+        <v>208</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>12</v>
+        <v>209</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>129</v>
+        <v>210</v>
       </c>
       <c r="B43" t="s">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>12</v>
+        <v>211</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>12</v>
+        <v>211</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>130</v>
+        <v>212</v>
       </c>
       <c r="B44" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="C44" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>12</v>
+        <v>213</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>12</v>
+        <v>214</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>12</v>
+        <v>215</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>132</v>
+        <v>216</v>
       </c>
       <c r="B45" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="C45" t="s">
-        <v>12</v>
+        <v>217</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>0.614391771436997</v>
       </c>
       <c r="G45" t="s">
-        <v>12</v>
+        <v>219</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>0.614391771436997</v>
       </c>
       <c r="I45" t="s">
-        <v>12</v>
+        <v>220</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>133</v>
+        <v>221</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>49</v>
       </c>
       <c r="C46" t="s">
-        <v>12</v>
+        <v>222</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>12</v>
+        <v>223</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>0.168121111090064</v>
       </c>
       <c r="G46" t="s">
-        <v>12</v>
+        <v>224</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.277184851907928</v>
       </c>
       <c r="I46" t="s">
-        <v>12</v>
+        <v>225</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>134</v>
+        <v>226</v>
       </c>
       <c r="B47" t="s">
-        <v>118</v>
+        <v>49</v>
       </c>
       <c r="C47" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>12</v>
+        <v>227</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" t="s">
-        <v>12</v>
+        <v>228</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>12</v>
+        <v>229</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>135</v>
+        <v>230</v>
       </c>
       <c r="B48" t="s">
-        <v>125</v>
+        <v>16</v>
       </c>
       <c r="C48" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>12</v>
+        <v>231</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>12</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>136</v>
+        <v>232</v>
       </c>
       <c r="B49" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="C49" t="s">
-        <v>12</v>
+        <v>233</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="s">
-        <v>12</v>
+        <v>234</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="s">
-        <v>12</v>
+        <v>235</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>137</v>
+        <v>236</v>
       </c>
       <c r="B50" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="C50" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>12</v>
+        <v>238</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>0.372647446451695</v>
       </c>
       <c r="G50" t="s">
-        <v>12</v>
+        <v>239</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>12</v>
+        <v>240</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>138</v>
+        <v>241</v>
       </c>
       <c r="B51" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="C51" t="s">
-        <v>12</v>
+        <v>242</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="s">
-        <v>12</v>
+        <v>243</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>12</v>
+        <v>244</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>12</v>
+        <v>245</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>139</v>
+        <v>246</v>
       </c>
       <c r="B52" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C52" t="s">
-        <v>12</v>
+        <v>247</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>12</v>
+        <v>248</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>0.372647446451695</v>
       </c>
       <c r="G52" t="s">
-        <v>12</v>
+        <v>249</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>0.372647446451695</v>
       </c>
       <c r="I52" t="s">
-        <v>12</v>
+        <v>250</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>140</v>
+        <v>251</v>
       </c>
       <c r="B53" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="C53" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>12</v>
+        <v>252</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>12</v>
+        <v>253</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>12</v>
+        <v>254</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>141</v>
+        <v>255</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="C54" t="s">
-        <v>12</v>
+        <v>256</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="s">
-        <v>12</v>
+        <v>257</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>12</v>
+        <v>258</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="I54" t="s">
-        <v>12</v>
+        <v>259</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>142</v>
+        <v>260</v>
       </c>
       <c r="B55" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
       <c r="C55" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>12</v>
+        <v>261</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>12</v>
+        <v>261</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>143</v>
+        <v>262</v>
       </c>
       <c r="B56" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
       <c r="C56" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>12</v>
+        <v>263</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>12</v>
+        <v>263</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>144</v>
+        <v>264</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="C57" t="s">
-        <v>12</v>
+        <v>265</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>12</v>
+        <v>266</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="G57" t="s">
-        <v>12</v>
+        <v>267</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>0.406145296366207</v>
       </c>
       <c r="I57" t="s">
-        <v>12</v>
+        <v>268</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
       <c r="B58" t="s">
-        <v>131</v>
+        <v>49</v>
       </c>
       <c r="C58" t="s">
-        <v>12</v>
+        <v>270</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>12</v>
+        <v>271</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>0.101970608421077</v>
       </c>
       <c r="G58" t="s">
-        <v>12</v>
+        <v>272</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>0.101970608421077</v>
       </c>
       <c r="I58" t="s">
-        <v>12</v>
+        <v>273</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>146</v>
+        <v>274</v>
       </c>
       <c r="B59" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C59" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>12</v>
+        <v>275</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>12</v>
+        <v>276</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>12</v>
+        <v>277</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>147</v>
+        <v>278</v>
       </c>
       <c r="B60" t="s">
+        <v>22</v>
+      </c>
+      <c r="C60" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="s">
+        <v>279</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>280</v>
+      </c>
+      <c r="B61" t="s">
         <v>16</v>
       </c>
-      <c r="C60" t="s">
-        <v>148</v>
-      </c>
-      <c r="D60" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="s">
-        <v>12</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="s">
-        <v>148</v>
+      <c r="C61" t="s">
+        <v>18</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="s">
+        <v>281</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>282</v>
+      </c>
+      <c r="B62" t="s">
+        <v>167</v>
+      </c>
+      <c r="C62" t="s">
+        <v>283</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="s">
+        <v>284</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.614391771436997</v>
+      </c>
+      <c r="G62" t="s">
+        <v>285</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.372647446451695</v>
+      </c>
+      <c r="I62" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>287</v>
+      </c>
+      <c r="B63" t="s">
+        <v>205</v>
+      </c>
+      <c r="C63" t="s">
+        <v>288</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="s">
+        <v>289</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.755081337596291</v>
+      </c>
+      <c r="G63" t="s">
+        <v>290</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.755081337596291</v>
+      </c>
+      <c r="I63" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>292</v>
+      </c>
+      <c r="B64" t="s">
+        <v>22</v>
+      </c>
+      <c r="C64" t="s">
+        <v>293</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="s">
+        <v>294</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="s">
+        <v>276</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>296</v>
+      </c>
+      <c r="B65" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65" t="s">
+        <v>297</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="s">
+        <v>298</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.101970608421077</v>
+      </c>
+      <c r="G65" t="s">
+        <v>299</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.101970608421077</v>
+      </c>
+      <c r="I65" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>301</v>
+      </c>
+      <c r="B66" t="s">
+        <v>173</v>
+      </c>
+      <c r="C66" t="s">
+        <v>302</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="s">
+        <v>303</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.755081337596291</v>
+      </c>
+      <c r="G66" t="s">
+        <v>304</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.755081337596291</v>
+      </c>
+      <c r="I66" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>306</v>
+      </c>
+      <c r="B67" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" t="s">
+        <v>307</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="s">
+        <v>308</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.233125285421556</v>
+      </c>
+      <c r="G67" t="s">
+        <v>309</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.384358616812558</v>
+      </c>
+      <c r="I67" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>311</v>
+      </c>
+      <c r="B68" t="s">
+        <v>22</v>
+      </c>
+      <c r="C68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="s">
+        <v>18</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="s">
+        <v>312</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>313</v>
+      </c>
+      <c r="B69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" t="s">
+        <v>314</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="s">
+        <v>315</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.384358616812558</v>
+      </c>
+      <c r="G69" t="s">
+        <v>316</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.233125285421556</v>
+      </c>
+      <c r="I69" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>318</v>
+      </c>
+      <c r="B70" t="s">
+        <v>22</v>
+      </c>
+      <c r="C70" t="s">
+        <v>319</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="s">
+        <v>18</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="s">
+        <v>276</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>321</v>
+      </c>
+      <c r="B71" t="s">
+        <v>22</v>
+      </c>
+      <c r="C71" t="s">
+        <v>18</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="s">
+        <v>18</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="s">
+        <v>322</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>323</v>
+      </c>
+      <c r="B72" t="s">
+        <v>324</v>
+      </c>
+      <c r="C72" t="s">
+        <v>325</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="s">
+        <v>18</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="s">
+        <v>326</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>328</v>
+      </c>
+      <c r="B73" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" t="s">
+        <v>329</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="s">
+        <v>18</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="s">
+        <v>330</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>332</v>
+      </c>
+      <c r="B74" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74" t="s">
+        <v>18</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="s">
+        <v>294</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="s">
+        <v>18</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>333</v>
+      </c>
+      <c r="B75" t="s">
+        <v>334</v>
+      </c>
+      <c r="C75" t="s">
+        <v>335</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="s">
+        <v>336</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="s">
+        <v>337</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>339</v>
+      </c>
+      <c r="B76"/>
+      <c r="C76" t="s">
+        <v>325</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="s">
+        <v>18</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="s">
+        <v>18</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>340</v>
+      </c>
+      <c r="B77"/>
+      <c r="C77" t="s">
+        <v>325</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="s">
+        <v>18</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="s">
+        <v>18</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>341</v>
+      </c>
+      <c r="B78" t="s">
+        <v>342</v>
+      </c>
+      <c r="C78" t="s">
+        <v>343</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="s">
+        <v>344</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="s">
+        <v>345</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>347</v>
+      </c>
+      <c r="B79" t="s">
+        <v>22</v>
+      </c>
+      <c r="C79" t="s">
+        <v>348</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="s">
+        <v>18</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="s">
+        <v>18</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>349</v>
+      </c>
+      <c r="B80" t="s">
+        <v>136</v>
+      </c>
+      <c r="C80" t="s">
+        <v>350</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="s">
+        <v>351</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.377540668798145</v>
+      </c>
+      <c r="G80" t="s">
+        <v>352</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.377540668798145</v>
+      </c>
+      <c r="I80" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>354</v>
+      </c>
+      <c r="B81" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" t="s">
+        <v>355</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="s">
+        <v>356</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.141397633162432</v>
+      </c>
+      <c r="G81" t="s">
+        <v>357</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.141397633162432</v>
+      </c>
+      <c r="I81" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>359</v>
+      </c>
+      <c r="B82" t="s">
+        <v>360</v>
+      </c>
+      <c r="C82" t="s">
+        <v>361</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="s">
+        <v>362</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="s">
+        <v>363</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>365</v>
+      </c>
+      <c r="B83" t="s">
+        <v>366</v>
+      </c>
+      <c r="C83" t="s">
+        <v>367</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="s">
+        <v>368</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="s">
+        <v>369</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>371</v>
+      </c>
+      <c r="B84" t="s">
+        <v>360</v>
+      </c>
+      <c r="C84" t="s">
+        <v>372</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="s">
+        <v>373</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="s">
+        <v>374</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>376</v>
+      </c>
+      <c r="B85" t="s">
+        <v>377</v>
+      </c>
+      <c r="C85" t="s">
+        <v>378</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="s">
+        <v>379</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="s">
+        <v>380</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>382</v>
+      </c>
+      <c r="B86" t="s">
+        <v>342</v>
+      </c>
+      <c r="C86" t="s">
+        <v>383</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="s">
+        <v>384</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.755081337596291</v>
+      </c>
+      <c r="G86" t="s">
+        <v>385</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.755081337596291</v>
+      </c>
+      <c r="I86" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>387</v>
+      </c>
+      <c r="B87" t="s">
+        <v>360</v>
+      </c>
+      <c r="C87" t="s">
+        <v>388</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="s">
+        <v>389</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.669620389113773</v>
+      </c>
+      <c r="G87" t="s">
+        <v>390</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.406145296366207</v>
+      </c>
+      <c r="I87" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>392</v>
+      </c>
+      <c r="B88" t="s">
+        <v>360</v>
+      </c>
+      <c r="C88" t="s">
+        <v>393</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="s">
+        <v>394</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.406145296366207</v>
+      </c>
+      <c r="G88" t="s">
+        <v>395</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.669620389113773</v>
+      </c>
+      <c r="I88" t="s">
+        <v>396</v>
       </c>
     </row>
   </sheetData>

--- a/content/post/drafts/weekly-picks/2025Ruka/ladies-points.xlsx
+++ b/content/post/drafts/weekly-picks/2025Ruka/ladies-points.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="396">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -59,6 +59,24 @@
     <t xml:space="preserve">197.850870088196</t>
   </si>
   <si>
+    <t xml:space="preserve">Jonna Sundling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4081168215604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6161383719809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4878053362589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.5120605298</t>
+  </si>
+  <si>
     <t xml:space="preserve">Therese Johaug</t>
   </si>
   <si>
@@ -95,142 +113,139 @@
     <t xml:space="preserve">176.433185878821</t>
   </si>
   <si>
+    <t xml:space="preserve">Rosie Brennan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6982578381954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7813210684529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.114864179351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.594443085999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Krista Pärmäkoski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6552296787326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4782167802621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6522512520971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.785697711092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ebba Andersson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.7726259215564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84238423884355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3339039374151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.948914097815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johanna Matintalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1543031025553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0838475644533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6174336018422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.855584268851</t>
+  </si>
+  <si>
     <t xml:space="preserve">Frida Karlsson</t>
   </si>
   <si>
-    <t xml:space="preserve">Sweden</t>
-  </si>
-  <si>
     <t xml:space="preserve">68.2027155548745</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3881589061507</t>
+    <t xml:space="preserve">14.7983889200383</t>
   </si>
   <si>
     <t xml:space="preserve">51.2329741353458</t>
   </si>
   <si>
-    <t xml:space="preserve">172.823848596371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ebba Andersson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.7726259215564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0025365955313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3339039374151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.109066454503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosie Brennan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6982578381954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7813210684529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.114864179351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.594443085999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Krista Pärmäkoski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6552296787326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4782167802621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6522512520971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.785697711092</t>
+    <t xml:space="preserve">134.234078610259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heidi Weng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.1662328944813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.037938907864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.204171802345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katharina Hennig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7069756049925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8450620444669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3672543115808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.91929196104</t>
   </si>
   <si>
     <t xml:space="preserve">Victoria Carl</t>
   </si>
   <si>
-    <t xml:space="preserve">Germany</t>
-  </si>
-  <si>
     <t xml:space="preserve">57.0037288919872</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2643633636339</t>
+    <t xml:space="preserve">8.19060155225158</t>
   </si>
   <si>
     <t xml:space="preserve">62.789340501309</t>
   </si>
   <si>
-    <t xml:space="preserve">142.05743275693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katharina Hennig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7069756049925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.610334659603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3672543115808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.684564576176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johanna Matintalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1543031025553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0838475644533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6174336018422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.855584268851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonna Sundling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4081168215604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9546255336323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4878053362589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.850547691452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heidi Weng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.1662328944813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.037938907864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.204171802345</t>
+    <t xml:space="preserve">127.983670945548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linn Svahn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5641268148047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9969401643004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65100859513019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.212075574235</t>
   </si>
   <si>
     <t xml:space="preserve">Teresa Stadlober</t>
@@ -293,6 +308,33 @@
     <t xml:space="preserve">93.5257957393434</t>
   </si>
   <si>
+    <t xml:space="preserve">Maja Dahlqvist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.3197221626229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1293024014614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4490245640843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laura Gimmler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1602676582945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4902418580198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57151909205403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2220286083683</t>
+  </si>
+  <si>
     <t xml:space="preserve">Delphine Claudel</t>
   </si>
   <si>
@@ -302,25 +344,40 @@
     <t xml:space="preserve">31.3878293340857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58949128264524</t>
+    <t xml:space="preserve">3.89472677899111</t>
   </si>
   <si>
     <t xml:space="preserve">51.4414360866402</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4187567033712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maja Dahlqvist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.3197221626229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1293024014614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4490245640843</t>
+    <t xml:space="preserve">86.7239921997171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emma Ribom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1811441371637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3852507816939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5069266507583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0733215696159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiril Udnes Weng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.822198906034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1256860470755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.9478849531095</t>
   </si>
   <si>
     <t xml:space="preserve">Sophia Laukli</t>
@@ -329,40 +386,13 @@
     <t xml:space="preserve">27.1858808890776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95546406476752</t>
+    <t xml:space="preserve">2.6733925472235</t>
   </si>
   <si>
     <t xml:space="preserve">53.7638382702879</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9051832241329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linn Svahn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5641268148047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6467969078394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65100859513019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8619323177743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiril Udnes Weng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.822198906034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1256860470755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.9478849531095</t>
+    <t xml:space="preserve">83.6231117065889</t>
   </si>
   <si>
     <t xml:space="preserve">Kristin Austgulen Fosnæs</t>
@@ -380,6 +410,24 @@
     <t xml:space="preserve">82.6383190229012</t>
   </si>
   <si>
+    <t xml:space="preserve">Katerina Janatova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czechia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8036942690328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5875041732528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0978351754783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.489033617764</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anne Kyllönen</t>
   </si>
   <si>
@@ -395,6 +443,21 @@
     <t xml:space="preserve">72.9671064833315</t>
   </si>
   <si>
+    <t xml:space="preserve">Julia Kern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88202153339065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2654276758687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2422713182569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3897205275162</t>
+  </si>
+  <si>
     <t xml:space="preserve">Silje Theodorsen</t>
   </si>
   <si>
@@ -419,24 +482,6 @@
     <t xml:space="preserve">68.6842177843071</t>
   </si>
   <si>
-    <t xml:space="preserve">Katerina Janatova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czechia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8036942690328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3047214036058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0978351754783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2062508481169</t>
-  </si>
-  <si>
     <t xml:space="preserve">Johanna Hagström</t>
   </si>
   <si>
@@ -449,19 +494,19 @@
     <t xml:space="preserve">65.1748586834949</t>
   </si>
   <si>
-    <t xml:space="preserve">Emma Ribom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1811441371637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0175062832809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5069266507583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7055770712029</t>
+    <t xml:space="preserve">Flora Dolci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5028365276629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80284838970979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6829000177084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9885849350811</t>
   </si>
   <si>
     <t xml:space="preserve">Moa Ilar</t>
@@ -476,19 +521,46 @@
     <t xml:space="preserve">63.4456166989302</t>
   </si>
   <si>
-    <t xml:space="preserve">Flora Dolci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5028365276629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30654414259781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6829000177084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.4922806879692</t>
+    <t xml:space="preserve">Julie Myhre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1902735873559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caterina Ganz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0626997729214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9084171800726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9321841154259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9033010684198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eva Urevc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6683053994398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4140431171777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5483603317947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6307088484121</t>
   </si>
   <si>
     <t xml:space="preserve">Pia Fink</t>
@@ -497,70 +569,13 @@
     <t xml:space="preserve">31.8479202308955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81918880229528</t>
+    <t xml:space="preserve">3.24439824817383</t>
   </si>
   <si>
     <t xml:space="preserve">17.5953406351831</t>
   </si>
   <si>
-    <t xml:space="preserve">58.2624496683739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julie Myhre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1902735873559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caterina Ganz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Italy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0626997729214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9084171800726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9321841154259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9033010684198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eva Urevc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6683053994398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4140431171777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5483603317947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6307088484121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julia Kern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88202153339065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.318412025805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2422713182569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4427048774525</t>
+    <t xml:space="preserve">52.6876591142524</t>
   </si>
   <si>
     <t xml:space="preserve">Anna Svendsen</t>
@@ -569,21 +584,6 @@
     <t xml:space="preserve">50.3304123876479</t>
   </si>
   <si>
-    <t xml:space="preserve">Laura Gimmler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1602676582945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6582393236582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57151909205403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.3900260740067</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jasmin Kähärä</t>
   </si>
   <si>
@@ -611,70 +611,112 @@
     <t xml:space="preserve">45.966268247928</t>
   </si>
   <si>
+    <t xml:space="preserve">Desiree Steiner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71590933007489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7131295107978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57580342205383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0048422629265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kathrine Stewart-Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5436016806224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4385364517734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.844343658367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8264817907627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ane Appelkvist Stenseth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9664756052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coletta Rydzek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0600434905039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8101773966144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02683579418623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8970566813046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicole Monsorno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6524033327357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66427434968176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3166776824174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anja Weber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.319071184153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0170157169424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19644880933393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5325357104294</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nadja Kälin</t>
   </si>
   <si>
     <t xml:space="preserve">14.5153474995435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6536112511615</t>
+    <t xml:space="preserve">5.08798336758948</t>
   </si>
   <si>
     <t xml:space="preserve">15.3228769994762</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4918357501812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kathrine Stewart-Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5436016806224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85130486134523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.844343658367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2392502003346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ane Appelkvist Stenseth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9664756052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicole Monsorno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6524033327357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66427434968176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3166776824174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anja Weber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.319071184153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0170157169424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19644880933393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5325357104294</t>
+    <t xml:space="preserve">34.9262078666091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisa Lohmann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7340937103877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3772694646279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1113631750156</t>
   </si>
   <si>
     <t xml:space="preserve">Katherine Sauerbrey</t>
@@ -683,25 +725,28 @@
     <t xml:space="preserve">25.8007441013787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33767138332315</t>
+    <t xml:space="preserve">1.41786936631834</t>
   </si>
   <si>
     <t xml:space="preserve">6.71807842668841</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8564939113903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisa Lohmann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7340937103877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3772694646279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1113631750156</t>
+    <t xml:space="preserve">33.9366918943854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francesca Franchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08884493506456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35565690881219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9415619954171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3860638392939</t>
   </si>
   <si>
     <t xml:space="preserve">Hedda Østberg Amundsen</t>
@@ -722,19 +767,19 @@
     <t xml:space="preserve">31.3035486545315</t>
   </si>
   <si>
-    <t xml:space="preserve">Francesca Franchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08884493506456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85490077780901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9415619954171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8853077082907</t>
+    <t xml:space="preserve">Melissa Gal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39481789560249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9842061939341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25116051614762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6301846056842</t>
   </si>
   <si>
     <t xml:space="preserve">Anni Alakoski</t>
@@ -752,21 +797,6 @@
     <t xml:space="preserve">27.2072238091715</t>
   </si>
   <si>
-    <t xml:space="preserve">Desiree Steiner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71590933007489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0725218382873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57580342205383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.364234590416</t>
-  </si>
-  <si>
     <t xml:space="preserve">Helen Hoffmann</t>
   </si>
   <si>
@@ -806,36 +836,6 @@
     <t xml:space="preserve">22.730823982568</t>
   </si>
   <si>
-    <t xml:space="preserve">Melissa Gal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39481789560249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3729707603707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25116051614762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0189491721208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coletta Rydzek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0600434905039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86650837537224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02683579418623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9533876600624</t>
-  </si>
-  <si>
     <t xml:space="preserve">Barbora Antosova</t>
   </si>
   <si>
@@ -860,34 +860,49 @@
     <t xml:space="preserve">17.6321147622695</t>
   </si>
   <si>
+    <t xml:space="preserve">Liliane Gagnon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.89306493940642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26786587348721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95897075496758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3337716890484</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anna Comarella</t>
   </si>
   <si>
     <t xml:space="preserve">6.10642294338102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03430404583511</t>
+    <t xml:space="preserve">4.26652107353962</t>
   </si>
   <si>
     <t xml:space="preserve">3.47220321667757</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6129302058937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liliane Gagnon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.89306493940642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99799256041574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95897075496758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0638983759769</t>
+    <t xml:space="preserve">13.8451472335982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Märta Rosenberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06716199869954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14949490893992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1625533883135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.379210295953</t>
   </si>
   <si>
     <t xml:space="preserve">Nora Kytäjä</t>
@@ -902,21 +917,6 @@
     <t xml:space="preserve">12.3779882630005</t>
   </si>
   <si>
-    <t xml:space="preserve">Märta Rosenberg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06716199869954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51679588459354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1625533883135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7465112716066</t>
-  </si>
-  <si>
     <t xml:space="preserve">Anja Mandeljc</t>
   </si>
   <si>
@@ -947,27 +947,27 @@
     <t xml:space="preserve">9.24697111447145</t>
   </si>
   <si>
+    <t xml:space="preserve">Haley Brewster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77501594518944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26373089885241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0082669293794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04701377342125</t>
+  </si>
+  <si>
     <t xml:space="preserve">Emmi Lämsä</t>
   </si>
   <si>
     <t xml:space="preserve">8.26541967304588</t>
   </si>
   <si>
-    <t xml:space="preserve">Haley Brewster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77501594518944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37302219549283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0082669293794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15630507006167</t>
-  </si>
-  <si>
     <t xml:space="preserve">Oona Kettunen</t>
   </si>
   <si>
@@ -1034,15 +1034,15 @@
     <t xml:space="preserve">Kamila YELGAZINOVA</t>
   </si>
   <si>
-    <t xml:space="preserve">Yelizaveta NOPRIIENKO</t>
+    <t xml:space="preserve">Yelizaveta Nopriienko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ukraine</t>
   </si>
   <si>
     <t xml:space="preserve">Anastasiia Nikon</t>
   </si>
   <si>
-    <t xml:space="preserve">Ukraine</t>
-  </si>
-  <si>
     <t xml:space="preserve">-4.07566363866445</t>
   </si>
   <si>
@@ -1067,13 +1067,10 @@
     <t xml:space="preserve">-2.80981013926786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6604078674652</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.335559479997712</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.813842791804943</t>
+    <t xml:space="preserve">-2.47425065927014</t>
   </si>
   <si>
     <t xml:space="preserve">Alayna Sonnesyn</t>
@@ -1160,34 +1157,34 @@
     <t xml:space="preserve">-21.4830443828482</t>
   </si>
   <si>
+    <t xml:space="preserve">Kseniya Shalygina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-21.4599065053224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.34164714660656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.66125332302153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-25.4628069749505</t>
+  </si>
+  <si>
     <t xml:space="preserve">Viktoriya Olekh</t>
   </si>
   <si>
     <t xml:space="preserve">-17.1278513639015</t>
   </si>
   <si>
-    <t xml:space="preserve">-1.06395545245009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.850857267663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-25.0426640840146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kseniya Shalygina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-21.4599065053224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.56328091768424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.66125332302153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-25.6844407460282</t>
+    <t xml:space="preserve">-1.40906071899097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9.07300568369477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-27.6099177665872</t>
   </si>
   <si>
     <t xml:space="preserve">Nadezhda Stepashkina</t>
@@ -1196,13 +1193,13 @@
     <t xml:space="preserve">-23.4238336897355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537505066642002</t>
+    <t xml:space="preserve">0.886196036481758</t>
   </si>
   <si>
     <t xml:space="preserve">-5.76574664452997</t>
   </si>
   <si>
-    <t xml:space="preserve">-28.6520752676235</t>
+    <t xml:space="preserve">-28.3033842977837</t>
   </si>
 </sst>
 </file>
@@ -1606,13 +1603,13 @@
         <v>18</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="s">
         <v>19</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.457000561256465</v>
       </c>
       <c r="I3" t="s">
         <v>20</v>
@@ -1635,7 +1632,7 @@
         <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="s">
         <v>25</v>
@@ -1670,7 +1667,7 @@
         <v>31</v>
       </c>
       <c r="H5" t="n">
-        <v>0.753466546065431</v>
+        <v>1</v>
       </c>
       <c r="I5" t="s">
         <v>32</v>
@@ -1681,7 +1678,7 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
@@ -1693,7 +1690,7 @@
         <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>0.753466546065431</v>
+        <v>1</v>
       </c>
       <c r="G6" t="s">
         <v>36</v>
@@ -1710,7 +1707,7 @@
         <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
         <v>39</v>
@@ -1739,7 +1736,7 @@
         <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
         <v>44</v>
@@ -1751,7 +1748,7 @@
         <v>45</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.101970608421077</v>
       </c>
       <c r="G8" t="s">
         <v>46</v>
@@ -1768,135 +1765,135 @@
         <v>48</v>
       </c>
       <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
         <v>49</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
         <v>50</v>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
         <v>51</v>
       </c>
-      <c r="F9" t="n">
-        <v>0.753466546065431</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
         <v>52</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
         <v>54</v>
       </c>
-      <c r="B10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
         <v>55</v>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="n">
+        <v>0.277184851907928</v>
+      </c>
+      <c r="G10" t="s">
         <v>56</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>57</v>
       </c>
       <c r="H10" t="n">
         <v>0.753466546065431</v>
       </c>
       <c r="I10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
       </c>
       <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
         <v>60</v>
       </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
         <v>61</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>62</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
         <v>64</v>
       </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
         <v>65</v>
       </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="F12" t="n">
+        <v>0.753466546065431</v>
+      </c>
+      <c r="G12" t="s">
         <v>66</v>
       </c>
-      <c r="F12" t="n">
-        <v>0.457000561256465</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="H12" t="n">
+        <v>0.753466546065431</v>
+      </c>
+      <c r="I12" t="s">
         <v>67</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.457000561256465</v>
-      </c>
-      <c r="I12" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
         <v>69</v>
       </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
         <v>70</v>
       </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>18</v>
-      </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.277184851907928</v>
       </c>
       <c r="G13" t="s">
         <v>71</v>
@@ -1913,36 +1910,36 @@
         <v>73</v>
       </c>
       <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
         <v>74</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
         <v>75</v>
       </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="F14" t="n">
+        <v>0.753466546065431</v>
+      </c>
+      <c r="G14" t="s">
         <v>76</v>
       </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="H14" t="n">
+        <v>0.168121111090064</v>
+      </c>
+      <c r="I14" t="s">
         <v>77</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" t="s">
         <v>79</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
       </c>
       <c r="C15" t="s">
         <v>80</v>
@@ -1951,39 +1948,39 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="s">
         <v>86</v>
@@ -2000,13 +1997,13 @@
         <v>88</v>
       </c>
       <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
         <v>89</v>
       </c>
-      <c r="C17" t="s">
-        <v>18</v>
-      </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="s">
         <v>90</v>
@@ -2032,91 +2029,91 @@
         <v>94</v>
       </c>
       <c r="C18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
         <v>95</v>
       </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
         <v>96</v>
       </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="s">
         <v>97</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
         <v>99</v>
       </c>
-      <c r="B19" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
         <v>100</v>
       </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
         <v>101</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" t="s">
         <v>103</v>
       </c>
-      <c r="B20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
         <v>104</v>
       </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
         <v>105</v>
       </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="H20" t="n">
+        <v>0.168121111090064</v>
+      </c>
+      <c r="I20" t="s">
         <v>106</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" t="s">
         <v>108</v>
-      </c>
-      <c r="B21" t="s">
-        <v>28</v>
       </c>
       <c r="C21" t="s">
         <v>109</v>
@@ -2128,13 +2125,13 @@
         <v>110</v>
       </c>
       <c r="F21" t="n">
-        <v>0.277184851907928</v>
+        <v>0.406145296366207</v>
       </c>
       <c r="G21" t="s">
         <v>111</v>
       </c>
       <c r="H21" t="n">
-        <v>0.168121111090064</v>
+        <v>1</v>
       </c>
       <c r="I21" t="s">
         <v>112</v>
@@ -2157,42 +2154,42 @@
         <v>115</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0.457000561256465</v>
       </c>
       <c r="G22" t="s">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.277184851907928</v>
       </c>
       <c r="I22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="s">
         <v>121</v>
@@ -2203,7 +2200,7 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C24" t="s">
         <v>123</v>
@@ -2215,7 +2212,7 @@
         <v>124</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0.384358616812558</v>
       </c>
       <c r="G24" t="s">
         <v>125</v>
@@ -2232,7 +2229,7 @@
         <v>127</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
         <v>128</v>
@@ -2241,317 +2238,317 @@
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>18</v>
+        <v>136</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>0.622459331201855</v>
       </c>
       <c r="I26" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B27" t="s">
-        <v>136</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F27" t="n">
-        <v>0.622459331201855</v>
+        <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H27" t="n">
-        <v>0.622459331201855</v>
+        <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0.633700227115744</v>
       </c>
       <c r="I28" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>147</v>
+        <v>24</v>
       </c>
       <c r="F29" t="n">
-        <v>0.168121111090064</v>
+        <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H29" t="n">
-        <v>0.277184851907928</v>
+        <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B30" t="s">
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>153</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>155</v>
+        <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F31" t="n">
-        <v>0.406145296366207</v>
+        <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F32" t="n">
-        <v>0.457000561256465</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="G32" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H32" t="n">
-        <v>0.457000561256465</v>
+        <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B33" t="s">
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>18</v>
+        <v>167</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B34" t="s">
-        <v>167</v>
+        <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>168</v>
+        <v>24</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="s">
         <v>170</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.614391771436997</v>
-      </c>
-      <c r="I34" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>171</v>
+      </c>
+      <c r="B35" t="s">
         <v>172</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>173</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
         <v>174</v>
       </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="s">
         <v>175</v>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="s">
+      <c r="H35" t="n">
+        <v>0.614391771436997</v>
+      </c>
+      <c r="I35" t="s">
         <v>176</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>177</v>
+      </c>
+      <c r="B36" t="s">
         <v>178</v>
-      </c>
-      <c r="B36" t="s">
-        <v>10</v>
       </c>
       <c r="C36" t="s">
         <v>179</v>
@@ -2563,13 +2560,13 @@
         <v>180</v>
       </c>
       <c r="F36" t="n">
-        <v>0.633700227115744</v>
+        <v>1</v>
       </c>
       <c r="G36" t="s">
         <v>181</v>
       </c>
       <c r="H36" t="n">
-        <v>0.633700227115744</v>
+        <v>1</v>
       </c>
       <c r="I36" t="s">
         <v>182</v>
@@ -2580,54 +2577,54 @@
         <v>183</v>
       </c>
       <c r="B37" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="C37" t="s">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0.168121111090064</v>
       </c>
       <c r="G37" t="s">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>0.457000561256465</v>
       </c>
       <c r="I37" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>186</v>
+        <v>24</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F38" t="n">
-        <v>0.277184851907928</v>
+        <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>188</v>
+        <v>24</v>
       </c>
       <c r="H38" t="n">
-        <v>0.168121111090064</v>
+        <v>0</v>
       </c>
       <c r="I38" t="s">
         <v>189</v>
@@ -2638,7 +2635,7 @@
         <v>190</v>
       </c>
       <c r="B39" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C39" t="s">
         <v>191</v>
@@ -2667,10 +2664,10 @@
         <v>195</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -2696,7 +2693,7 @@
         <v>199</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C41" t="s">
         <v>200</v>
@@ -2714,7 +2711,7 @@
         <v>202</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0.372647446451695</v>
       </c>
       <c r="I41" t="s">
         <v>203</v>
@@ -2737,7 +2734,7 @@
         <v>207</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G42" t="s">
         <v>208</v>
@@ -2754,10 +2751,10 @@
         <v>210</v>
       </c>
       <c r="B43" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -2769,7 +2766,7 @@
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2783,54 +2780,54 @@
         <v>212</v>
       </c>
       <c r="B44" t="s">
-        <v>167</v>
+        <v>63</v>
       </c>
       <c r="C44" t="s">
-        <v>18</v>
+        <v>213</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0.457000561256465</v>
       </c>
       <c r="G44" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0.101970608421077</v>
       </c>
       <c r="I44" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="C45" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="s">
         <v>218</v>
       </c>
       <c r="F45" t="n">
-        <v>0.614391771436997</v>
+        <v>1</v>
       </c>
       <c r="G45" t="s">
         <v>219</v>
       </c>
       <c r="H45" t="n">
-        <v>0.614391771436997</v>
+        <v>1</v>
       </c>
       <c r="I45" t="s">
         <v>220</v>
@@ -2841,7 +2838,7 @@
         <v>221</v>
       </c>
       <c r="B46" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="C46" t="s">
         <v>222</v>
@@ -2853,13 +2850,13 @@
         <v>223</v>
       </c>
       <c r="F46" t="n">
-        <v>0.168121111090064</v>
+        <v>0.614391771436997</v>
       </c>
       <c r="G46" t="s">
         <v>224</v>
       </c>
       <c r="H46" t="n">
-        <v>0.277184851907928</v>
+        <v>0.614391771436997</v>
       </c>
       <c r="I46" t="s">
         <v>225</v>
@@ -2870,170 +2867,170 @@
         <v>226</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="C47" t="s">
-        <v>18</v>
+        <v>227</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>0.372647446451695</v>
       </c>
       <c r="G47" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B48" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>18</v>
+        <v>233</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B49" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C49" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D49" t="n">
         <v>1</v>
       </c>
       <c r="E49" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>0.101970608421077</v>
       </c>
       <c r="G49" t="s">
-        <v>18</v>
+        <v>238</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>0.277184851907928</v>
       </c>
       <c r="I49" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B50" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C50" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D50" t="n">
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F50" t="n">
-        <v>0.372647446451695</v>
+        <v>0.614391771436997</v>
       </c>
       <c r="G50" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H50" t="n">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B51" t="s">
         <v>22</v>
       </c>
       <c r="C51" t="s">
-        <v>242</v>
+        <v>24</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>244</v>
+        <v>24</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B52" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F52" t="n">
-        <v>0.372647446451695</v>
+        <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>249</v>
+        <v>24</v>
       </c>
       <c r="H52" t="n">
-        <v>0.372647446451695</v>
+        <v>0</v>
       </c>
       <c r="I52" t="s">
         <v>250</v>
@@ -3044,170 +3041,170 @@
         <v>251</v>
       </c>
       <c r="B53" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="C53" t="s">
-        <v>18</v>
+        <v>252</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0.406145296366207</v>
       </c>
       <c r="I53" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B54" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="C54" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D54" t="n">
         <v>1</v>
       </c>
       <c r="E54" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H54" t="n">
-        <v>0.669620389113773</v>
+        <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B55" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C55" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>18</v>
+        <v>262</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H55" t="n">
         <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B56" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="C56" t="s">
-        <v>18</v>
+        <v>266</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>18</v>
+        <v>268</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="I56" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B57" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="C57" t="s">
-        <v>265</v>
+        <v>24</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>266</v>
+        <v>24</v>
       </c>
       <c r="F57" t="n">
-        <v>0.669620389113773</v>
+        <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="H57" t="n">
-        <v>0.406145296366207</v>
+        <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B58" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="C58" t="s">
-        <v>270</v>
+        <v>24</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F58" t="n">
-        <v>0.101970608421077</v>
+        <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>272</v>
+        <v>24</v>
       </c>
       <c r="H58" t="n">
-        <v>0.101970608421077</v>
+        <v>0</v>
       </c>
       <c r="I58" t="s">
         <v>273</v>
@@ -3218,10 +3215,10 @@
         <v>274</v>
       </c>
       <c r="B59" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C59" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -3247,10 +3244,10 @@
         <v>278</v>
       </c>
       <c r="B60" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C60" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -3262,7 +3259,7 @@
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -3276,16 +3273,16 @@
         <v>280</v>
       </c>
       <c r="B61" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C61" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -3305,7 +3302,7 @@
         <v>282</v>
       </c>
       <c r="B62" t="s">
-        <v>167</v>
+        <v>205</v>
       </c>
       <c r="C62" t="s">
         <v>283</v>
@@ -3317,13 +3314,13 @@
         <v>284</v>
       </c>
       <c r="F62" t="n">
-        <v>0.614391771436997</v>
+        <v>1</v>
       </c>
       <c r="G62" t="s">
         <v>285</v>
       </c>
       <c r="H62" t="n">
-        <v>0.372647446451695</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="I62" t="s">
         <v>286</v>
@@ -3334,7 +3331,7 @@
         <v>287</v>
       </c>
       <c r="B63" t="s">
-        <v>205</v>
+        <v>172</v>
       </c>
       <c r="C63" t="s">
         <v>288</v>
@@ -3346,13 +3343,13 @@
         <v>289</v>
       </c>
       <c r="F63" t="n">
-        <v>0.755081337596291</v>
+        <v>0.372647446451695</v>
       </c>
       <c r="G63" t="s">
         <v>290</v>
       </c>
       <c r="H63" t="n">
-        <v>0.755081337596291</v>
+        <v>0.372647446451695</v>
       </c>
       <c r="I63" t="s">
         <v>291</v>
@@ -3363,7 +3360,7 @@
         <v>292</v>
       </c>
       <c r="B64" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C64" t="s">
         <v>293</v>
@@ -3375,42 +3372,42 @@
         <v>294</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>0.168121111090064</v>
       </c>
       <c r="G64" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>0.101970608421077</v>
       </c>
       <c r="I64" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B65" t="s">
         <v>28</v>
       </c>
       <c r="C65" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F65" t="n">
-        <v>0.101970608421077</v>
+        <v>1</v>
       </c>
       <c r="G65" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="H65" t="n">
-        <v>0.101970608421077</v>
+        <v>1</v>
       </c>
       <c r="I65" t="s">
         <v>300</v>
@@ -3421,7 +3418,7 @@
         <v>301</v>
       </c>
       <c r="B66" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C66" t="s">
         <v>302</v>
@@ -3479,54 +3476,54 @@
         <v>311</v>
       </c>
       <c r="B68" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>18</v>
+        <v>312</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" t="s">
-        <v>18</v>
+        <v>313</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>0.633700227115744</v>
       </c>
       <c r="G68" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0.233125285421556</v>
       </c>
       <c r="I68" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B69" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C69" t="s">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>315</v>
+        <v>24</v>
       </c>
       <c r="F69" t="n">
-        <v>0.384358616812558</v>
+        <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H69" t="n">
-        <v>0.233125285421556</v>
+        <v>1</v>
       </c>
       <c r="I69" t="s">
         <v>317</v>
@@ -3537,7 +3534,7 @@
         <v>318</v>
       </c>
       <c r="B70" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C70" t="s">
         <v>319</v>
@@ -3546,7 +3543,7 @@
         <v>1</v>
       </c>
       <c r="E70" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -3566,16 +3563,16 @@
         <v>321</v>
       </c>
       <c r="B71" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C71" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -3604,7 +3601,7 @@
         <v>1</v>
       </c>
       <c r="E72" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -3624,7 +3621,7 @@
         <v>328</v>
       </c>
       <c r="B73" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C73" t="s">
         <v>329</v>
@@ -3633,7 +3630,7 @@
         <v>1</v>
       </c>
       <c r="E73" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -3653,28 +3650,28 @@
         <v>332</v>
       </c>
       <c r="B74" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C74" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="F74" t="n">
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="75">
@@ -3718,13 +3715,13 @@
         <v>1</v>
       </c>
       <c r="E76" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3737,7 +3734,9 @@
       <c r="A77" t="s">
         <v>340</v>
       </c>
-      <c r="B77"/>
+      <c r="B77" t="s">
+        <v>341</v>
+      </c>
       <c r="C77" t="s">
         <v>325</v>
       </c>
@@ -3745,13 +3744,13 @@
         <v>1</v>
       </c>
       <c r="E77" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3762,10 +3761,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
+        <v>342</v>
+      </c>
+      <c r="B78" t="s">
         <v>341</v>
-      </c>
-      <c r="B78" t="s">
-        <v>342</v>
       </c>
       <c r="C78" t="s">
         <v>343</v>
@@ -3794,7 +3793,7 @@
         <v>347</v>
       </c>
       <c r="B79" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C79" t="s">
         <v>348</v>
@@ -3803,13 +3802,13 @@
         <v>1</v>
       </c>
       <c r="E79" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3823,7 +3822,7 @@
         <v>349</v>
       </c>
       <c r="B80" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C80" t="s">
         <v>350</v>
@@ -3832,251 +3831,251 @@
         <v>1</v>
       </c>
       <c r="E80" t="s">
+        <v>24</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="s">
         <v>351</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.377540668798145</v>
-      </c>
-      <c r="G80" t="s">
-        <v>352</v>
       </c>
       <c r="H80" t="n">
         <v>0.377540668798145</v>
       </c>
       <c r="I80" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B81" t="s">
         <v>10</v>
       </c>
       <c r="C81" t="s">
+        <v>354</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="s">
         <v>355</v>
-      </c>
-      <c r="D81" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" t="s">
-        <v>356</v>
       </c>
       <c r="F81" t="n">
         <v>0.141397633162432</v>
       </c>
       <c r="G81" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H81" t="n">
         <v>0.141397633162432</v>
       </c>
       <c r="I81" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
+        <v>358</v>
+      </c>
+      <c r="B82" t="s">
         <v>359</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>360</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="s">
         <v>361</v>
       </c>
-      <c r="D82" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" t="s">
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="s">
         <v>362</v>
       </c>
-      <c r="F82" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" t="s">
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="s">
         <v>363</v>
-      </c>
-      <c r="H82" t="n">
-        <v>1</v>
-      </c>
-      <c r="I82" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>364</v>
+      </c>
+      <c r="B83" t="s">
         <v>365</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>366</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="s">
         <v>367</v>
       </c>
-      <c r="D83" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" t="s">
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="s">
         <v>368</v>
       </c>
-      <c r="F83" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" t="s">
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="s">
         <v>369</v>
-      </c>
-      <c r="H83" t="n">
-        <v>1</v>
-      </c>
-      <c r="I83" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
+        <v>370</v>
+      </c>
+      <c r="B84" t="s">
+        <v>359</v>
+      </c>
+      <c r="C84" t="s">
         <v>371</v>
       </c>
-      <c r="B84" t="s">
-        <v>360</v>
-      </c>
-      <c r="C84" t="s">
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="s">
         <v>372</v>
       </c>
-      <c r="D84" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" t="s">
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="s">
         <v>373</v>
       </c>
-      <c r="F84" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" t="s">
+      <c r="H84" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" t="s">
         <v>374</v>
-      </c>
-      <c r="H84" t="n">
-        <v>1</v>
-      </c>
-      <c r="I84" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
+        <v>375</v>
+      </c>
+      <c r="B85" t="s">
         <v>376</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>377</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="s">
         <v>378</v>
       </c>
-      <c r="D85" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" t="s">
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="s">
         <v>379</v>
       </c>
-      <c r="F85" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" t="s">
+      <c r="H85" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" t="s">
         <v>380</v>
-      </c>
-      <c r="H85" t="n">
-        <v>1</v>
-      </c>
-      <c r="I85" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
+        <v>381</v>
+      </c>
+      <c r="B86" t="s">
+        <v>359</v>
+      </c>
+      <c r="C86" t="s">
         <v>382</v>
       </c>
-      <c r="B86" t="s">
-        <v>342</v>
-      </c>
-      <c r="C86" t="s">
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="s">
         <v>383</v>
       </c>
-      <c r="D86" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" t="s">
+      <c r="F86" t="n">
+        <v>0.406145296366207</v>
+      </c>
+      <c r="G86" t="s">
         <v>384</v>
       </c>
-      <c r="F86" t="n">
-        <v>0.755081337596291</v>
-      </c>
-      <c r="G86" t="s">
+      <c r="H86" t="n">
+        <v>0.406145296366207</v>
+      </c>
+      <c r="I86" t="s">
         <v>385</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0.755081337596291</v>
-      </c>
-      <c r="I86" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
+        <v>386</v>
+      </c>
+      <c r="B87" t="s">
+        <v>341</v>
+      </c>
+      <c r="C87" t="s">
         <v>387</v>
       </c>
-      <c r="B87" t="s">
-        <v>360</v>
-      </c>
-      <c r="C87" t="s">
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="s">
         <v>388</v>
       </c>
-      <c r="D87" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" t="s">
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="s">
         <v>389</v>
       </c>
-      <c r="F87" t="n">
-        <v>0.669620389113773</v>
-      </c>
-      <c r="G87" t="s">
+      <c r="H87" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" t="s">
         <v>390</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0.406145296366207</v>
-      </c>
-      <c r="I87" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
+        <v>391</v>
+      </c>
+      <c r="B88" t="s">
+        <v>359</v>
+      </c>
+      <c r="C88" t="s">
         <v>392</v>
       </c>
-      <c r="B88" t="s">
-        <v>360</v>
-      </c>
-      <c r="C88" t="s">
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="s">
         <v>393</v>
       </c>
-      <c r="D88" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" t="s">
+      <c r="F88" t="n">
+        <v>0.669620389113773</v>
+      </c>
+      <c r="G88" t="s">
         <v>394</v>
-      </c>
-      <c r="F88" t="n">
-        <v>0.406145296366207</v>
-      </c>
-      <c r="G88" t="s">
-        <v>395</v>
       </c>
       <c r="H88" t="n">
         <v>0.669620389113773</v>
       </c>
       <c r="I88" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>

--- a/content/post/drafts/weekly-picks/2025Ruka/ladies-points.xlsx
+++ b/content/post/drafts/weekly-picks/2025Ruka/ladies-points.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="362">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -863,16 +863,13 @@
     <t xml:space="preserve">Liliane Gagnon</t>
   </si>
   <si>
-    <t xml:space="preserve">-1.89306493940642</t>
-  </si>
-  <si>
     <t xml:space="preserve">9.26786587348721</t>
   </si>
   <si>
     <t xml:space="preserve">7.95897075496758</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3337716890484</t>
+    <t xml:space="preserve">17.2268366284548</t>
   </si>
   <si>
     <t xml:space="preserve">Anna Comarella</t>
@@ -890,6 +887,18 @@
     <t xml:space="preserve">13.8451472335982</t>
   </si>
   <si>
+    <t xml:space="preserve">Anja Mandeljc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15164756711344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28697469964535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4386222667588</t>
+  </si>
+  <si>
     <t xml:space="preserve">Märta Rosenberg</t>
   </si>
   <si>
@@ -917,21 +926,6 @@
     <t xml:space="preserve">12.3779882630005</t>
   </si>
   <si>
-    <t xml:space="preserve">Anja Mandeljc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.72963767364509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15164756711344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28697469964535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7089845931137</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sydney Palmer-Leger</t>
   </si>
   <si>
@@ -998,37 +992,58 @@
     <t xml:space="preserve">6.35972270600612</t>
   </si>
   <si>
+    <t xml:space="preserve">Anastasiia Nikon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ukraine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89562494997936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14993240488253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0455573548619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teesi Tuul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80873915452093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15212039848492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96085955300585</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vilma Nissinen</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.233748889400793</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.72459449577808</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49084560637728</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ella-Noora Haapalehto</t>
   </si>
   <si>
-    <t xml:space="preserve">Teesi Tuul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.3191225889495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80873915452093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15212039848492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64173696405635</t>
+    <t xml:space="preserve">Darya Ryazhko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kazakhstan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89472438896276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angelina Shuryga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69916890824031</t>
   </si>
   <si>
     <t xml:space="preserve">Kamila YELGAZINOVA</t>
@@ -1037,169 +1052,52 @@
     <t xml:space="preserve">Yelizaveta Nopriienko</t>
   </si>
   <si>
-    <t xml:space="preserve">Ukraine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anastasiia Nikon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.07566363866445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89562494997936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14993240488253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.969893716197443</t>
+    <t xml:space="preserve">Kitija Auzina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55075517758024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alayna Sonnesyn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03119809319374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381970249240256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.413168342434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nadezhda Stepashkina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.886196036481758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbora Havlickova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335559479997712</t>
   </si>
   <si>
     <t xml:space="preserve">Elsa Torvinen</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.175962770175843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbora Havlickova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.80981013926786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335559479997712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.47425065927014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alayna Sonnesyn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-10.7356841725455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03119809319374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381970249240256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-9.32251583011153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angelina Shuryga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kazakhstan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-10.7879541015177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69916890824031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.76503695470362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-11.853822147981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitija Auzina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latvia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-14.8844441835301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55075517758024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.28899508869889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-16.6226840946488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darya Ryazhko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-14.836643303959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89472438896276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.68971126949382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-19.6316301844901</t>
-  </si>
-  <si>
     <t xml:space="preserve">Katya Galstyan</t>
   </si>
   <si>
     <t xml:space="preserve">Armenia</t>
   </si>
   <si>
-    <t xml:space="preserve">-14.6821365329454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.319258260812212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.48164958909061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-21.4830443828482</t>
+    <t xml:space="preserve">Viktoriya Olekh</t>
   </si>
   <si>
     <t xml:space="preserve">Kseniya Shalygina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-21.4599065053224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.34164714660656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.66125332302153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-25.4628069749505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viktoriya Olekh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-17.1278513639015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.40906071899097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-9.07300568369477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-27.6099177665872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nadezhda Stepashkina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-23.4238336897355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.886196036481758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.76574664452997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-28.3033842977837</t>
   </si>
 </sst>
 </file>
@@ -3305,204 +3203,204 @@
         <v>205</v>
       </c>
       <c r="C62" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="s">
         <v>283</v>
       </c>
-      <c r="D62" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" t="s">
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="s">
         <v>284</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="s">
-        <v>285</v>
       </c>
       <c r="H62" t="n">
         <v>0.755081337596291</v>
       </c>
       <c r="I62" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B63" t="s">
         <v>172</v>
       </c>
       <c r="C63" t="s">
+        <v>287</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="s">
         <v>288</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" t="s">
-        <v>289</v>
       </c>
       <c r="F63" t="n">
         <v>0.372647446451695</v>
       </c>
       <c r="G63" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H63" t="n">
         <v>0.372647446451695</v>
       </c>
       <c r="I63" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>291</v>
+      </c>
+      <c r="B64" t="s">
+        <v>178</v>
+      </c>
+      <c r="C64" t="s">
+        <v>24</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="s">
         <v>292</v>
       </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="s">
+      <c r="F64" t="n">
+        <v>0.755081337596291</v>
+      </c>
+      <c r="G64" t="s">
         <v>293</v>
       </c>
-      <c r="D64" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="H64" t="n">
+        <v>0.755081337596291</v>
+      </c>
+      <c r="I64" t="s">
         <v>294</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.168121111090064</v>
-      </c>
-      <c r="G64" t="s">
-        <v>295</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.101970608421077</v>
-      </c>
-      <c r="I64" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>295</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="s">
+        <v>296</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="s">
         <v>297</v>
       </c>
-      <c r="B65" t="s">
-        <v>28</v>
-      </c>
-      <c r="C65" t="s">
+      <c r="F65" t="n">
+        <v>0.168121111090064</v>
+      </c>
+      <c r="G65" t="s">
         <v>298</v>
       </c>
-      <c r="D65" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="H65" t="n">
+        <v>0.101970608421077</v>
+      </c>
+      <c r="I65" t="s">
         <v>299</v>
-      </c>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" t="s">
-        <v>276</v>
-      </c>
-      <c r="H65" t="n">
-        <v>1</v>
-      </c>
-      <c r="I65" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>300</v>
+      </c>
+      <c r="B66" t="s">
+        <v>28</v>
+      </c>
+      <c r="C66" t="s">
         <v>301</v>
       </c>
-      <c r="B66" t="s">
-        <v>178</v>
-      </c>
-      <c r="C66" t="s">
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="s">
         <v>302</v>
       </c>
-      <c r="D66" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="s">
+        <v>276</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="s">
         <v>303</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0.755081337596291</v>
-      </c>
-      <c r="G66" t="s">
-        <v>304</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.755081337596291</v>
-      </c>
-      <c r="I66" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B67" t="s">
         <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D67" t="n">
         <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F67" t="n">
         <v>0.233125285421556</v>
       </c>
       <c r="G67" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H67" t="n">
         <v>0.384358616812558</v>
       </c>
       <c r="I67" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B68" t="s">
         <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D68" t="n">
         <v>1</v>
       </c>
       <c r="E68" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F68" t="n">
         <v>0.633700227115744</v>
       </c>
       <c r="G68" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H68" t="n">
         <v>0.233125285421556</v>
       </c>
       <c r="I68" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B69" t="s">
         <v>28</v>
@@ -3520,24 +3418,24 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H69" t="n">
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B70" t="s">
         <v>28</v>
       </c>
       <c r="C70" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D70" t="n">
         <v>1</v>
@@ -3555,12 +3453,12 @@
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B71" t="s">
         <v>28</v>
@@ -3578,120 +3476,120 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H71" t="n">
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
+        <v>321</v>
+      </c>
+      <c r="B72" t="s">
+        <v>322</v>
+      </c>
+      <c r="C72" t="s">
         <v>323</v>
       </c>
-      <c r="B72" t="s">
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="s">
+        <v>24</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="s">
         <v>324</v>
       </c>
-      <c r="C72" t="s">
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" t="s">
         <v>325</v>
-      </c>
-      <c r="D72" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" t="s">
-        <v>24</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="s">
-        <v>326</v>
-      </c>
-      <c r="H72" t="n">
-        <v>1</v>
-      </c>
-      <c r="I72" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
+        <v>326</v>
+      </c>
+      <c r="B73" t="s">
+        <v>327</v>
+      </c>
+      <c r="C73" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="s">
         <v>328</v>
       </c>
-      <c r="B73" t="s">
-        <v>28</v>
-      </c>
-      <c r="C73" t="s">
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="s">
         <v>329</v>
       </c>
-      <c r="D73" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" t="s">
-        <v>24</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="s">
+      <c r="H73" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" t="s">
         <v>330</v>
-      </c>
-      <c r="H73" t="n">
-        <v>1</v>
-      </c>
-      <c r="I73" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>331</v>
+      </c>
+      <c r="B74" t="s">
         <v>332</v>
       </c>
-      <c r="B74" t="s">
-        <v>28</v>
-      </c>
       <c r="C74" t="s">
         <v>24</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>299</v>
+        <v>333</v>
       </c>
       <c r="F74" t="n">
         <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>24</v>
+        <v>334</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" t="s">
-        <v>299</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B75" t="s">
-        <v>334</v>
+        <v>28</v>
       </c>
       <c r="C75" t="s">
-        <v>335</v>
+        <v>24</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>336</v>
+        <v>24</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="s">
         <v>337</v>
@@ -3700,25 +3598,27 @@
         <v>1</v>
       </c>
       <c r="I75" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>339</v>
-      </c>
-      <c r="B76"/>
+        <v>338</v>
+      </c>
+      <c r="B76" t="s">
+        <v>28</v>
+      </c>
       <c r="C76" t="s">
-        <v>325</v>
+        <v>24</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>24</v>
+        <v>302</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" t="s">
         <v>24</v>
@@ -3727,36 +3627,36 @@
         <v>0</v>
       </c>
       <c r="I76" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
+        <v>339</v>
+      </c>
+      <c r="B77" t="s">
         <v>340</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
+        <v>24</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="s">
         <v>341</v>
       </c>
-      <c r="C77" t="s">
-        <v>325</v>
-      </c>
-      <c r="D77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" t="s">
-        <v>24</v>
-      </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" t="s">
         <v>24</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78">
@@ -3764,39 +3664,37 @@
         <v>342</v>
       </c>
       <c r="B78" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C78" t="s">
+        <v>24</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="s">
         <v>343</v>
       </c>
-      <c r="D78" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" t="s">
-        <v>344</v>
-      </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" t="s">
-        <v>345</v>
+        <v>24</v>
       </c>
       <c r="H78" t="n">
         <v>1</v>
       </c>
       <c r="I78" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>347</v>
-      </c>
-      <c r="B79" t="s">
-        <v>28</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="B79"/>
       <c r="C79" t="s">
-        <v>348</v>
+        <v>323</v>
       </c>
       <c r="D79" t="n">
         <v>1</v>
@@ -3814,18 +3712,18 @@
         <v>0</v>
       </c>
       <c r="I79" t="s">
-        <v>348</v>
+        <v>323</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B80" t="s">
-        <v>133</v>
+        <v>327</v>
       </c>
       <c r="C80" t="s">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="D80" t="n">
         <v>1</v>
@@ -3837,245 +3735,245 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>351</v>
+        <v>24</v>
       </c>
       <c r="H80" t="n">
-        <v>0.377540668798145</v>
+        <v>0</v>
       </c>
       <c r="I80" t="s">
-        <v>352</v>
+        <v>323</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B81" t="s">
-        <v>10</v>
+        <v>347</v>
       </c>
       <c r="C81" t="s">
-        <v>354</v>
+        <v>24</v>
       </c>
       <c r="D81" t="n">
         <v>1</v>
       </c>
       <c r="E81" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="F81" t="n">
-        <v>0.141397633162432</v>
+        <v>1</v>
       </c>
       <c r="G81" t="s">
-        <v>356</v>
+        <v>24</v>
       </c>
       <c r="H81" t="n">
-        <v>0.141397633162432</v>
+        <v>1</v>
       </c>
       <c r="I81" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="B82" t="s">
-        <v>359</v>
+        <v>10</v>
       </c>
       <c r="C82" t="s">
-        <v>360</v>
+        <v>24</v>
       </c>
       <c r="D82" t="n">
         <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>0.141397633162432</v>
       </c>
       <c r="G82" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>0.141397633162432</v>
       </c>
       <c r="I82" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="B83" t="s">
-        <v>365</v>
+        <v>340</v>
       </c>
       <c r="C83" t="s">
-        <v>366</v>
+        <v>24</v>
       </c>
       <c r="D83" t="n">
         <v>1</v>
       </c>
       <c r="E83" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="G83" t="s">
-        <v>368</v>
+        <v>24</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="I83" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="B84" t="s">
-        <v>359</v>
+        <v>133</v>
       </c>
       <c r="C84" t="s">
-        <v>371</v>
+        <v>24</v>
       </c>
       <c r="D84" t="n">
         <v>1</v>
       </c>
       <c r="E84" t="s">
-        <v>372</v>
+        <v>24</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>0.377540668798145</v>
       </c>
       <c r="I84" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="B85" t="s">
-        <v>376</v>
+        <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>377</v>
+        <v>24</v>
       </c>
       <c r="D85" t="n">
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>378</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>379</v>
+        <v>24</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" t="s">
-        <v>380</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>381</v>
+        <v>358</v>
       </c>
       <c r="B86" t="s">
         <v>359</v>
       </c>
       <c r="C86" t="s">
-        <v>382</v>
+        <v>24</v>
       </c>
       <c r="D86" t="n">
         <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>383</v>
+        <v>24</v>
       </c>
       <c r="F86" t="n">
-        <v>0.406145296366207</v>
+        <v>1</v>
       </c>
       <c r="G86" t="s">
-        <v>384</v>
+        <v>24</v>
       </c>
       <c r="H86" t="n">
-        <v>0.406145296366207</v>
+        <v>1</v>
       </c>
       <c r="I86" t="s">
-        <v>385</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="B87" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="C87" t="s">
-        <v>387</v>
+        <v>24</v>
       </c>
       <c r="D87" t="n">
         <v>1</v>
       </c>
       <c r="E87" t="s">
-        <v>388</v>
+        <v>24</v>
       </c>
       <c r="F87" t="n">
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>389</v>
+        <v>24</v>
       </c>
       <c r="H87" t="n">
         <v>1</v>
       </c>
       <c r="I87" t="s">
-        <v>390</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>391</v>
+        <v>361</v>
       </c>
       <c r="B88" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="C88" t="s">
-        <v>392</v>
+        <v>24</v>
       </c>
       <c r="D88" t="n">
         <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>393</v>
+        <v>24</v>
       </c>
       <c r="F88" t="n">
-        <v>0.669620389113773</v>
+        <v>0.406145296366207</v>
       </c>
       <c r="G88" t="s">
-        <v>394</v>
+        <v>24</v>
       </c>
       <c r="H88" t="n">
-        <v>0.669620389113773</v>
+        <v>0.406145296366207</v>
       </c>
       <c r="I88" t="s">
-        <v>395</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
